--- a/Grupo07/docs/income_dictionary.xlsx
+++ b/Grupo07/docs/income_dictionary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leydi\Documents\Machine-Learning-para-Finanzas_2026_0\Grupo07\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3FF69D-8E7C-4AD1-AC60-0AC130FE92E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC3109B-CA32-45C7-B587-A66B2346A07F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{54952E9C-228E-4F9B-929C-B363D3D5F4DE}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -198,12 +197,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -233,7 +238,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -242,6 +247,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -730,13 +741,13 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -744,7 +755,7 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
